--- a/data/processed/positivacao/2022-06_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-06_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B945" t="inlineStr"/>
@@ -36687,7 +36687,7 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr"/>
@@ -65605,7 +65605,7 @@
     <row r="2512">
       <c r="A2512" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2512" t="inlineStr"/>
@@ -67276,12 +67276,12 @@
       <c r="A2577" t="inlineStr"/>
       <c r="B2577" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 12 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 19.539,70
+          <t>Vendedor 1 - VENDEDOR 01: positivou 12 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 19.539,70
 Vendedor 18 - LOJA: positivou 75 cliente(s), não positivou 759 cliente(s) - Total vendido: R$ 57.438,61
-Vendedor 3 - FERNANDA: positivou 106 cliente(s), não positivou 347 cliente(s) - Total vendido: R$ 87.819,30
-Vendedor 4 - DANIELA: positivou 39 cliente(s), não positivou 621 cliente(s) - Total vendido: R$ 20.969,97
+Vendedor 3 - VENDEDOR 03: positivou 106 cliente(s), não positivou 347 cliente(s) - Total vendido: R$ 87.819,30
+Vendedor 4 - VENDEDOR 04: positivou 39 cliente(s), não positivou 621 cliente(s) - Total vendido: R$ 20.969,97
 Vendedor 5 - SITE: positivou 7 cliente(s), não positivou 444 cliente(s) - Total vendido: R$ 1.563,12
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2577" t="inlineStr"/>
